--- a/data/b2_bonsucesso/B2 Bonsucesso 08-2026.xlsx
+++ b/data/b2_bonsucesso/B2 Bonsucesso 08-2026.xlsx
@@ -4918,25 +4918,25 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1222.69</v>
+        <v>1114.18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>1229.99</v>
+        <v>2946.33</v>
       </c>
     </row>
     <row r="4">
@@ -4954,48 +4954,48 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>66602.88</v>
+        <v>65080.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>2613.97</v>
+        <v>4250.41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>4332.12</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -5004,47 +5004,47 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1672.8</v>
+        <v>693.62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>3600</v>
+        <v>1435.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46246</v>
+        <v>46249</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1289.16</v>
+        <v>9881.92</v>
       </c>
     </row>
     <row r="10">
@@ -5053,16 +5053,16 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>10104.83</v>
+        <v>2562.28</v>
       </c>
     </row>
     <row r="11">
@@ -5071,16 +5071,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>2000.85</v>
+        <v>799.37</v>
       </c>
     </row>
     <row r="12">
@@ -5089,34 +5089,34 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>4169.9</v>
+        <v>4322.79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>4298.6</v>
+        <v>22811.79</v>
       </c>
     </row>
     <row r="14">
@@ -5125,52 +5125,52 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>23229.2</v>
+        <v>1994.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>1422.57</v>
+        <v>4524.43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>4354.93</v>
+        <v>2122.48</v>
       </c>
     </row>
     <row r="17">
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>4451.19</v>
+        <v>4211.13</v>
       </c>
     </row>
     <row r="18">
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>593.11</v>
+        <v>579.87</v>
       </c>
     </row>
   </sheetData>
